--- a/reports/集团总公司_利润表_2026-11.xlsx
+++ b/reports/集团总公司_利润表_2026-11.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>218941407</v>
+        <v>238356172</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>166772278</v>
+        <v>180907971</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1887292482</v>
+        <v>2049563616</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>680337</v>
+        <v>881276</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>7795451</v>
+        <v>10096752</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>588163</v>
+        <v>769807</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>6762063</v>
+        <v>8834395</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>499238</v>
+        <v>648712</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>5732409</v>
+        <v>7456399</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>460660</v>
+        <v>597873</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>5274484</v>
+        <v>6880917</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>249731</v>
+        <v>328450</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2865540</v>
+        <v>3783121</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>199354</v>
+        <v>258662</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>2292412</v>
+        <v>2979649</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>216263924</v>
+        <v>234871392</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>164094795</v>
+        <v>177423191</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>84405582</v>
+        <v>92032247</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>926645103</v>
+        <v>1017608823</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1547330</v>
+        <v>2750922</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>17768920</v>
+        <v>31509772</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1401923</v>
+        <v>2003162</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>16053591</v>
+        <v>22919063</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>75066429</v>
+        <v>79353583</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>876955737</v>
+        <v>922989866</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1591444</v>
+        <v>2007973</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>18334764</v>
+        <v>22938241</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>699423</v>
+        <v>1002969</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>8026349</v>
+        <v>11471734</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2509522</v>
+        <v>3006841</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>28669490</v>
+        <v>34425572</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1097955</v>
+        <v>1501196</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>12607448</v>
+        <v>17210317</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>51995098</v>
+        <v>51997479</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>588405017</v>
+        <v>588452206</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>174031</v>
+        <v>174591</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1933620</v>
+        <v>1926565</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3166673</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>36462320</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2109458</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>24299655</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>158206298</v>
+        <v>179060287</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>126990352</v>
+        <v>133889891</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>100068509</v>
+        <v>106695602</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1166525063</v>
+        <v>1246457937</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>26921843</v>
+        <v>27194289</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>310539091</v>
+        <v>310595429</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5301684</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>60720666</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1699155</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>19436151</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1063092</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>12151781</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1276200</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>14587154</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>956811</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>10943459</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>637219</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>7296892</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>530207</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>6080930</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>2946339</v>
+        <v>2943223</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>33825558</v>
+        <v>33837897</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1392870</v>
+        <v>1387612</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>15938516</v>
+        <v>15948311</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3592213</v>
+        <v>3580721</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>41254318</v>
+        <v>41250073</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>23176328</v>
+        <v>23189201</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>276878580</v>
+        <v>276840848</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>354838</v>
+        <v>2842270</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>3993264</v>
+        <v>32637688</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1146228</v>
+        <v>1150613</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>12738136</v>
+        <v>12678492</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1178673</v>
+        <v>1100005</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>13190818</v>
+        <v>12114531</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>121859</v>
+        <v>123517</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>1366316</v>
+        <v>1358391</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>492020</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>5401018</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>929387</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>10629609</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>328822</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>3603285</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>246687</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>2703463</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>410960</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>4507076</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1327300</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>15202048</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>218592</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>2404137</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>163656</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1802811</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>272312</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>3003798</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>190384</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>2101872</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>135906</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>1500752</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>108740</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>1200206</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>81624</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>899958</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>58057626</v>
+        <v>59105132</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>62807447</v>
+        <v>63326331</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>530403</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>6072475</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>136898</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>1500862</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>213391</v>
+        <v>217160</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>2389951</v>
+        <v>2379647</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>57844235</v>
+        <v>59418375</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7232739</v>
+        <v>7340820</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>80809432</v>
+        <v>80504802</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>50611496</v>
+        <v>52077555</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>50611496</v>
+        <v>52077555</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>50611496</v>
+        <v>52077555</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>50611496</v>
+        <v>52077555</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>50611496</v>
+        <v>52077555</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
